--- a/data/raw/gastos.xlsx
+++ b/data/raw/gastos.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="26">
   <si>
     <t xml:space="preserve">tipo</t>
   </si>
@@ -40,10 +40,64 @@
     <t xml:space="preserve">fecha</t>
   </si>
   <si>
+    <t xml:space="preserve">frecuencia</t>
+  </si>
+  <si>
     <t xml:space="preserve">fijo</t>
   </si>
   <si>
-    <t xml:space="preserve">variable</t>
+    <t xml:space="preserve">entretenimiento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spotify</t>
+  </si>
+  <si>
+    <t xml:space="preserve">suscripcion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mensual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">salida</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hbo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">credito</t>
+  </si>
+  <si>
+    <t xml:space="preserve">steam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prestamo nu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pantalla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cuentas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cuota de manejo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cuenta nu </t>
+  </si>
+  <si>
+    <t xml:space="preserve">cuenta bancolombia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mensual </t>
+  </si>
+  <si>
+    <t xml:space="preserve">finanzas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ahorro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ahorro y fondo de emergencia</t>
   </si>
 </sst>
 </file>
@@ -58,6 +112,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -117,9 +172,25 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -245,37 +316,195 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:G3"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="25.51"/>
+  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B1" s="0" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="0" t="s">
-        <v>6</v>
+      <c r="A2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="1" t="n">
+        <v>25000</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="0" t="s">
-        <v>7</v>
+      <c r="A3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>200000</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>14500</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>26300</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>30700</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="0" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7" s="0" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="0" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G8" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" s="0" t="n">
+        <v>200000</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9" s="0" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
